--- a/artfynd/A 6134-2023 artfynd.xlsx
+++ b/artfynd/A 6134-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122182856</v>
+        <v>122182855</v>
       </c>
       <c r="B2" t="n">
-        <v>79686</v>
+        <v>78645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318037</v>
+        <v>318023</v>
       </c>
       <c r="R2" t="n">
-        <v>6609350</v>
+        <v>6609330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122182855</v>
+        <v>122182856</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>79686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318023</v>
+        <v>318037</v>
       </c>
       <c r="R3" t="n">
-        <v>6609330</v>
+        <v>6609350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 6134-2023 artfynd.xlsx
+++ b/artfynd/A 6134-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122182855</v>
+        <v>122182857</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318023</v>
+        <v>318056</v>
       </c>
       <c r="R2" t="n">
-        <v>6609330</v>
+        <v>6609367</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122182856</v>
+        <v>122182855</v>
       </c>
       <c r="B3" t="n">
-        <v>79686</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318037</v>
+        <v>318023</v>
       </c>
       <c r="R3" t="n">
-        <v>6609350</v>
+        <v>6609330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122182857</v>
+        <v>122182856</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>79687</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>318056</v>
+        <v>318037</v>
       </c>
       <c r="R4" t="n">
-        <v>6609367</v>
+        <v>6609350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 6134-2023 artfynd.xlsx
+++ b/artfynd/A 6134-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122182857</v>
+        <v>122182855</v>
       </c>
       <c r="B2" t="n">
         <v>78646</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318056</v>
+        <v>318023</v>
       </c>
       <c r="R2" t="n">
-        <v>6609367</v>
+        <v>6609330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122182855</v>
+        <v>122182857</v>
       </c>
       <c r="B3" t="n">
         <v>78646</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318023</v>
+        <v>318056</v>
       </c>
       <c r="R3" t="n">
-        <v>6609330</v>
+        <v>6609367</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 6134-2023 artfynd.xlsx
+++ b/artfynd/A 6134-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122182856</v>
+        <v>122182855</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>318037</v>
+        <v>318023</v>
       </c>
       <c r="R2" t="n">
-        <v>6609350</v>
+        <v>6609330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,16 +775,11 @@
         <v>122182857</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122182855</v>
+        <v>122182856</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>318023</v>
+        <v>318037</v>
       </c>
       <c r="R4" t="n">
-        <v>6609330</v>
+        <v>6609350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
